--- a/物品清单.xlsx
+++ b/物品清单.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="66">
   <si>
     <t>itemNum</t>
   </si>
@@ -167,6 +167,15 @@
   </si>
   <si>
     <t>223.8.10</t>
+  </si>
+  <si>
+    <t>给洛库斯的感谢信1</t>
+  </si>
+  <si>
+    <t>synChro关于洛库斯的帖子</t>
+  </si>
+  <si>
+    <t>给洛库斯的感谢信2</t>
   </si>
   <si>
     <t>权重</t>
@@ -1157,7 +1166,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="20.5" customWidth="1"/>
@@ -1367,6 +1376,9 @@
       <c r="C13">
         <v>1</v>
       </c>
+      <c r="E13" t="s">
+        <v>16</v>
+      </c>
       <c r="F13" t="s">
         <v>17</v>
       </c>
@@ -1449,6 +1461,39 @@
       </c>
       <c r="F17" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>102015</v>
+      </c>
+      <c r="B18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>102016</v>
+      </c>
+      <c r="B19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>102017</v>
+      </c>
+      <c r="B20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1474,10 +1519,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1485,7 +1530,7 @@
         <v>201001</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1493,7 +1538,7 @@
         <v>201002</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1501,7 +1546,7 @@
         <v>201003</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1509,7 +1554,7 @@
         <v>201004</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1517,7 +1562,7 @@
         <v>201005</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1528,7 +1573,7 @@
         <v>201006</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1539,7 +1584,7 @@
         <v>201007</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C8">
         <v>5</v>
@@ -1550,7 +1595,7 @@
         <v>201008</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C9">
         <v>3</v>
@@ -1579,7 +1624,7 @@
         <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1587,7 +1632,7 @@
         <v>301001</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1595,7 +1640,7 @@
         <v>301002</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1603,7 +1648,7 @@
         <v>301003</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1611,7 +1656,7 @@
         <v>301004</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1619,7 +1664,7 @@
         <v>301005</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1627,7 +1672,7 @@
         <v>301006</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1635,7 +1680,7 @@
         <v>301007</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/物品清单.xlsx
+++ b/物品清单.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MMGA\TerminalCity\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="一级资料" sheetId="1" r:id="rId1"/>
@@ -29,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="67">
   <si>
     <t>itemNum</t>
   </si>
@@ -206,6 +211,9 @@
   </si>
   <si>
     <t>戴利克的日记</t>
+  </si>
+  <si>
+    <t>凛的手稿</t>
   </si>
   <si>
     <t>首脑争论</t>
@@ -1505,7 +1513,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -1599,6 +1607,14 @@
       </c>
       <c r="C9">
         <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>201009</v>
+      </c>
+      <c r="B10" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1632,7 +1648,7 @@
         <v>301001</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1640,7 +1656,7 @@
         <v>301002</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1648,7 +1664,7 @@
         <v>301003</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1656,7 +1672,7 @@
         <v>301004</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1664,7 +1680,7 @@
         <v>301005</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1672,7 +1688,7 @@
         <v>301006</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1680,7 +1696,7 @@
         <v>301007</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/物品清单.xlsx
+++ b/物品清单.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="1"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="一级资料" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="68">
   <si>
     <t>itemNum</t>
   </si>
@@ -181,6 +181,9 @@
   </si>
   <si>
     <t>给洛库斯的感谢信2</t>
+  </si>
+  <si>
+    <t>ID卡-克索里</t>
   </si>
   <si>
     <t>权重</t>
@@ -1174,7 +1177,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="20.5" customWidth="1"/>
@@ -1502,6 +1505,17 @@
       </c>
       <c r="C20">
         <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21">
+        <v>101003</v>
+      </c>
+      <c r="B21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1527,10 +1541,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1538,7 +1552,7 @@
         <v>201001</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1546,7 +1560,7 @@
         <v>201002</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1554,7 +1568,7 @@
         <v>201003</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1562,7 +1576,7 @@
         <v>201004</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1570,7 +1584,7 @@
         <v>201005</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1581,7 +1595,7 @@
         <v>201006</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1592,7 +1606,7 @@
         <v>201007</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8">
         <v>5</v>
@@ -1603,7 +1617,7 @@
         <v>201008</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9">
         <v>3</v>
@@ -1614,7 +1628,7 @@
         <v>201009</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1640,7 +1654,7 @@
         <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1648,7 +1662,7 @@
         <v>301001</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1656,7 +1670,7 @@
         <v>301002</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1664,7 +1678,7 @@
         <v>301003</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1672,7 +1686,7 @@
         <v>301004</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1680,7 +1694,7 @@
         <v>301005</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1688,7 +1702,7 @@
         <v>301006</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1696,7 +1710,7 @@
         <v>301007</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/物品清单.xlsx
+++ b/物品清单.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="70">
   <si>
     <t>itemNum</t>
   </si>
@@ -72,7 +72,7 @@
     <t>凛/Lyn</t>
   </si>
   <si>
-    <t>第二三位：01为ID卡，02为非ID卡（后期会进行进一步的分类细化）</t>
+    <t>第二三位：00为特殊物品，01为ID卡，02为非ID卡（后期会进行进一步的分类细化）</t>
   </si>
   <si>
     <t>TeraCity立项书(1)</t>
@@ -90,6 +90,9 @@
     <t>TC建立</t>
   </si>
   <si>
+    <t>所有itemType为10的物品都不会在合成背包里显示</t>
+  </si>
+  <si>
     <t>ID卡-罗奈尔德</t>
   </si>
   <si>
@@ -184,6 +187,9 @@
   </si>
   <si>
     <t>ID卡-克索里</t>
+  </si>
+  <si>
+    <t>志愿者#404的记录</t>
   </si>
   <si>
     <t>权重</t>
@@ -1177,7 +1183,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="20.5" customWidth="1"/>
@@ -1267,19 +1273,22 @@
       <c r="F4" t="s">
         <v>17</v>
       </c>
+      <c r="P4" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5">
         <v>101002</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1287,13 +1296,13 @@
         <v>102003</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1301,7 +1310,7 @@
         <v>102004</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1312,13 +1321,13 @@
         <v>101005</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1326,13 +1335,13 @@
         <v>101006</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1340,16 +1349,16 @@
         <v>102007</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1357,7 +1366,7 @@
         <v>102008</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1368,13 +1377,13 @@
         <v>101009</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1382,7 +1391,7 @@
         <v>102010</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1399,19 +1408,19 @@
         <v>102011</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1419,22 +1428,22 @@
         <v>102012</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1442,19 +1451,19 @@
         <v>102013</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1462,16 +1471,16 @@
         <v>102014</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1479,7 +1488,7 @@
         <v>102015</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1490,7 +1499,7 @@
         <v>102016</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -1501,7 +1510,7 @@
         <v>102017</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1512,10 +1521,21 @@
         <v>101003</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C21">
         <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22">
+        <v>100001</v>
+      </c>
+      <c r="B22" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1541,10 +1561,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1552,7 +1572,7 @@
         <v>201001</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1560,7 +1580,7 @@
         <v>201002</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1568,7 +1588,7 @@
         <v>201003</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1576,7 +1596,7 @@
         <v>201004</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1584,7 +1604,7 @@
         <v>201005</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1595,7 +1615,7 @@
         <v>201006</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1606,7 +1626,7 @@
         <v>201007</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C8">
         <v>5</v>
@@ -1617,7 +1637,7 @@
         <v>201008</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C9">
         <v>3</v>
@@ -1628,7 +1648,7 @@
         <v>201009</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1654,7 +1674,7 @@
         <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1662,7 +1682,7 @@
         <v>301001</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1670,7 +1690,7 @@
         <v>301002</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1678,7 +1698,7 @@
         <v>301003</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1686,7 +1706,7 @@
         <v>301004</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1694,7 +1714,7 @@
         <v>301005</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1702,7 +1722,7 @@
         <v>301006</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1710,7 +1730,7 @@
         <v>301007</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/物品清单.xlsx
+++ b/物品清单.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="71">
   <si>
     <t>itemNum</t>
   </si>
@@ -190,6 +190,9 @@
   </si>
   <si>
     <t>志愿者#404的记录</t>
+  </si>
+  <si>
+    <t>志愿者#402的笔记</t>
   </si>
   <si>
     <t>权重</t>
@@ -1183,7 +1186,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="20.5" customWidth="1"/>
@@ -1535,6 +1538,17 @@
         <v>51</v>
       </c>
       <c r="C22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23">
+        <v>100002</v>
+      </c>
+      <c r="B23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23">
         <v>10</v>
       </c>
     </row>
@@ -1561,10 +1575,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1572,7 +1586,7 @@
         <v>201001</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1580,7 +1594,7 @@
         <v>201002</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1588,7 +1602,7 @@
         <v>201003</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1596,7 +1610,7 @@
         <v>201004</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1604,7 +1618,7 @@
         <v>201005</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1615,7 +1629,7 @@
         <v>201006</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1626,7 +1640,7 @@
         <v>201007</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C8">
         <v>5</v>
@@ -1637,7 +1651,7 @@
         <v>201008</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C9">
         <v>3</v>
@@ -1648,7 +1662,7 @@
         <v>201009</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1674,7 +1688,7 @@
         <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1682,7 +1696,7 @@
         <v>301001</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1690,7 +1704,7 @@
         <v>301002</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1698,7 +1712,7 @@
         <v>301003</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1706,7 +1720,7 @@
         <v>301004</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1714,7 +1728,7 @@
         <v>301005</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1722,7 +1736,7 @@
         <v>301006</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1730,7 +1744,7 @@
         <v>301007</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
